--- a/modules/data-sync/scripts/dbpasn-employees.xlsx
+++ b/modules/data-sync/scripts/dbpasn-employees.xlsx
@@ -640,7 +640,7 @@
         <v>6388526744</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
